--- a/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0002T0006Z000C1N7_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0002T0006Z000C1N7_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>56.00942815732509</v>
+        <v>9.101532075565327</v>
       </c>
       <c r="D2" t="n">
-        <v>16.87000211174776</v>
+        <v>2.741375343159011</v>
       </c>
       <c r="E2" t="n">
-        <v>14.79285669079825</v>
+        <v>2.403839212254715</v>
       </c>
       <c r="F2" t="n">
-        <v>9.663265577019624</v>
+        <v>1.570280656265688</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>52.89911725554257</v>
+        <v>8.596106554025669</v>
       </c>
       <c r="D3" t="n">
-        <v>2.446751819905485</v>
+        <v>0.3975971707346413</v>
       </c>
       <c r="E3" t="n">
-        <v>14.79285669079825</v>
+        <v>2.403839212254715</v>
       </c>
       <c r="F3" t="n">
-        <v>9.663265577019624</v>
+        <v>1.570280656265688</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>36.0378758750764</v>
+        <v>5.856154829699916</v>
       </c>
       <c r="D4" t="n">
-        <v>17.49994003936735</v>
+        <v>2.843740256397195</v>
       </c>
       <c r="E4" t="n">
-        <v>14.79285669079825</v>
+        <v>2.403839212254715</v>
       </c>
       <c r="F4" t="n">
-        <v>9.663265577019624</v>
+        <v>1.570280656265688</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>52.42136716536981</v>
+        <v>8.518472164372595</v>
       </c>
       <c r="D5" t="n">
-        <v>22.95534768911908</v>
+        <v>3.73024399948185</v>
       </c>
       <c r="E5" t="n">
-        <v>14.79285669079825</v>
+        <v>2.403839212254715</v>
       </c>
       <c r="F5" t="n">
-        <v>9.663265577019624</v>
+        <v>1.570280656265688</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>47.60775298673943</v>
+        <v>7.736259860345158</v>
       </c>
       <c r="D6" t="n">
-        <v>6.951886612522541</v>
+        <v>1.129681574534913</v>
       </c>
       <c r="E6" t="n">
-        <v>14.79285669079825</v>
+        <v>2.403839212254715</v>
       </c>
       <c r="F6" t="n">
-        <v>9.663265577019624</v>
+        <v>1.570280656265688</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>35.13946815508483</v>
+        <v>5.710163575201284</v>
       </c>
       <c r="D7" t="n">
-        <v>16.65082580534671</v>
+        <v>2.705759193368841</v>
       </c>
       <c r="E7" t="n">
-        <v>14.79285669079825</v>
+        <v>2.403839212254715</v>
       </c>
       <c r="F7" t="n">
-        <v>9.663265577019624</v>
+        <v>1.570280656265688</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>45.2397356965316</v>
+        <v>7.351457050686385</v>
       </c>
       <c r="D8" t="n">
-        <v>24.10828854041277</v>
+        <v>3.917596887817075</v>
       </c>
       <c r="E8" t="n">
-        <v>14.79285669079825</v>
+        <v>2.403839212254715</v>
       </c>
       <c r="F8" t="n">
-        <v>9.663265577019624</v>
+        <v>1.570280656265688</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>49.03488895929871</v>
+        <v>7.968169455886041</v>
       </c>
       <c r="D9" t="n">
-        <v>43.96416107393338</v>
+        <v>7.144176174514174</v>
       </c>
       <c r="E9" t="n">
-        <v>14.79285669079825</v>
+        <v>2.403839212254715</v>
       </c>
       <c r="F9" t="n">
-        <v>9.663265577019624</v>
+        <v>1.570280656265688</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>43.07071008065261</v>
+        <v>6.99899038810605</v>
       </c>
       <c r="D10" t="n">
-        <v>4.156587094831417</v>
+        <v>0.6754454029101052</v>
       </c>
       <c r="E10" t="n">
-        <v>14.79285669079825</v>
+        <v>2.403839212254715</v>
       </c>
       <c r="F10" t="n">
-        <v>9.663265577019624</v>
+        <v>1.570280656265688</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>43.26205661575468</v>
+        <v>7.030084200060136</v>
       </c>
       <c r="D11" t="n">
-        <v>7.875126700367522</v>
+        <v>1.279708088809722</v>
       </c>
       <c r="E11" t="n">
-        <v>14.79285669079825</v>
+        <v>2.403839212254715</v>
       </c>
       <c r="F11" t="n">
-        <v>9.663265577019624</v>
+        <v>1.570280656265688</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>43.01023188964665</v>
+        <v>6.989162682067581</v>
       </c>
       <c r="D12" t="n">
-        <v>20.18043607061056</v>
+        <v>3.279320861474217</v>
       </c>
       <c r="E12" t="n">
-        <v>14.79285669079825</v>
+        <v>2.403839212254715</v>
       </c>
       <c r="F12" t="n">
-        <v>9.663265577019624</v>
+        <v>1.570280656265688</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>52.97215201300478</v>
+        <v>8.607974702113276</v>
       </c>
       <c r="D13" t="n">
-        <v>15.62849960808778</v>
+        <v>2.539631186314265</v>
       </c>
       <c r="E13" t="n">
-        <v>14.79285669079825</v>
+        <v>2.403839212254715</v>
       </c>
       <c r="F13" t="n">
-        <v>9.663265577019624</v>
+        <v>1.570280656265688</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>54.79566808915492</v>
+        <v>8.904296064487674</v>
       </c>
       <c r="D14" t="n">
-        <v>20.52437575177379</v>
+        <v>3.335211059663242</v>
       </c>
       <c r="E14" t="n">
-        <v>14.79285669079825</v>
+        <v>2.403839212254715</v>
       </c>
       <c r="F14" t="n">
-        <v>9.663265577019624</v>
+        <v>1.570280656265688</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>18.0187910786852</v>
+        <v>2.928053550286345</v>
       </c>
       <c r="D15" t="n">
-        <v>16.8430991817361</v>
+        <v>2.737003617032117</v>
       </c>
       <c r="E15" t="n">
-        <v>14.79285669079825</v>
+        <v>2.403839212254715</v>
       </c>
       <c r="F15" t="n">
-        <v>9.663265577019624</v>
+        <v>1.570280656265688</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>58.39529360206453</v>
+        <v>9.489235210335487</v>
       </c>
       <c r="D16" t="n">
-        <v>23.69071548096427</v>
+        <v>3.849741265656694</v>
       </c>
       <c r="E16" t="n">
-        <v>14.79285669079825</v>
+        <v>2.403839212254715</v>
       </c>
       <c r="F16" t="n">
-        <v>9.663265577019624</v>
+        <v>1.570280656265688</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>40.43971778709032</v>
+        <v>6.571454140402178</v>
       </c>
       <c r="D17" t="n">
-        <v>41.96657244344114</v>
+        <v>6.819568022059185</v>
       </c>
       <c r="E17" t="n">
-        <v>14.79285669079825</v>
+        <v>2.403839212254715</v>
       </c>
       <c r="F17" t="n">
-        <v>9.663265577019624</v>
+        <v>1.570280656265688</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>39.20044799536371</v>
+        <v>6.370072799246604</v>
       </c>
       <c r="D18" t="n">
-        <v>13.11599464958063</v>
+        <v>2.131349130556853</v>
       </c>
       <c r="E18" t="n">
-        <v>14.79285669079825</v>
+        <v>2.403839212254715</v>
       </c>
       <c r="F18" t="n">
-        <v>9.663265577019624</v>
+        <v>1.570280656265688</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>13.52732767412601</v>
+        <v>2.198190747045476</v>
       </c>
       <c r="D19" t="n">
-        <v>12.70614243118933</v>
+        <v>2.064748145068266</v>
       </c>
       <c r="E19" t="n">
-        <v>14.79285669079825</v>
+        <v>2.403839212254715</v>
       </c>
       <c r="F19" t="n">
-        <v>9.663265577019624</v>
+        <v>1.570280656265688</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>26.83859171627653</v>
+        <v>4.361271153894936</v>
       </c>
       <c r="D20" t="n">
-        <v>27.83327498682082</v>
+        <v>4.522907185358384</v>
       </c>
       <c r="E20" t="n">
-        <v>14.79285669079825</v>
+        <v>2.403839212254715</v>
       </c>
       <c r="F20" t="n">
-        <v>9.663265577019624</v>
+        <v>1.570280656265688</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>41.34242627360382</v>
+        <v>6.718144269460621</v>
       </c>
       <c r="D21" t="n">
-        <v>11.17545915985629</v>
+        <v>1.816012113476648</v>
       </c>
       <c r="E21" t="n">
-        <v>14.79285669079825</v>
+        <v>2.403839212254715</v>
       </c>
       <c r="F21" t="n">
-        <v>9.663265577019624</v>
+        <v>1.570280656265688</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>62.73017550868269</v>
+        <v>10.19365352016094</v>
       </c>
       <c r="D22" t="n">
-        <v>27.1542150828446</v>
+        <v>4.412559950962248</v>
       </c>
       <c r="E22" t="n">
-        <v>14.79285669079825</v>
+        <v>2.403839212254715</v>
       </c>
       <c r="F22" t="n">
-        <v>9.663265577019624</v>
+        <v>1.570280656265688</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>46.49494669224945</v>
+        <v>7.555428837490536</v>
       </c>
       <c r="D23" t="n">
-        <v>15.25819451966713</v>
+        <v>2.479456609445908</v>
       </c>
       <c r="E23" t="n">
-        <v>14.79285669079825</v>
+        <v>2.403839212254715</v>
       </c>
       <c r="F23" t="n">
-        <v>9.663265577019624</v>
+        <v>1.570280656265688</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>49.06493420752015</v>
+        <v>7.973051808722025</v>
       </c>
       <c r="D24" t="n">
-        <v>23.17612302189976</v>
+        <v>3.766119991058711</v>
       </c>
       <c r="E24" t="n">
-        <v>14.79285669079825</v>
+        <v>2.403839212254715</v>
       </c>
       <c r="F24" t="n">
-        <v>9.663265577019624</v>
+        <v>1.570280656265688</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>42.69518667365446</v>
+        <v>6.93796783446885</v>
       </c>
       <c r="D25" t="n">
-        <v>20.77181203346957</v>
+        <v>3.375419455438805</v>
       </c>
       <c r="E25" t="n">
-        <v>14.79285669079825</v>
+        <v>2.403839212254715</v>
       </c>
       <c r="F25" t="n">
-        <v>9.663265577019624</v>
+        <v>1.570280656265688</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>52.41095428713759</v>
+        <v>8.516780071659859</v>
       </c>
       <c r="D26" t="n">
-        <v>8.769722339733676</v>
+        <v>1.425079880206722</v>
       </c>
       <c r="E26" t="n">
-        <v>14.79285669079825</v>
+        <v>2.403839212254715</v>
       </c>
       <c r="F26" t="n">
-        <v>9.663265577019624</v>
+        <v>1.570280656265688</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>76.4720217394111</v>
+        <v>12.4267035326543</v>
       </c>
       <c r="D27" t="n">
-        <v>24.89138729586283</v>
+        <v>4.044850435577709</v>
       </c>
       <c r="E27" t="n">
-        <v>14.79285669079825</v>
+        <v>2.403839212254715</v>
       </c>
       <c r="F27" t="n">
-        <v>9.663265577019624</v>
+        <v>1.570280656265688</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>63.23627910960758</v>
+        <v>10.27589535531123</v>
       </c>
       <c r="D28" t="n">
-        <v>10.2018831148564</v>
+        <v>1.657806006164164</v>
       </c>
       <c r="E28" t="n">
-        <v>14.79285669079825</v>
+        <v>2.403839212254715</v>
       </c>
       <c r="F28" t="n">
-        <v>9.663265577019624</v>
+        <v>1.570280656265688</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>75.84416728095603</v>
+        <v>12.32467718315536</v>
       </c>
       <c r="D29" t="n">
-        <v>6.664497159149856</v>
+        <v>1.082980788361852</v>
       </c>
       <c r="E29" t="n">
-        <v>14.79285669079825</v>
+        <v>2.403839212254715</v>
       </c>
       <c r="F29" t="n">
-        <v>9.663265577019624</v>
+        <v>1.570280656265688</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>77.50996956185934</v>
+        <v>12.59537005380214</v>
       </c>
       <c r="D30" t="n">
-        <v>11.35004438689075</v>
+        <v>1.844382212869747</v>
       </c>
       <c r="E30" t="n">
-        <v>14.79285669079825</v>
+        <v>2.403839212254715</v>
       </c>
       <c r="F30" t="n">
-        <v>9.663265577019624</v>
+        <v>1.570280656265688</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
